--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹99 (23.35%) 30 ↓ / 106 ↑</t>
+          <t>₹110 (25.94%) 30 ↓ / 110 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>13-Sep 13:37</t>
+          <t>13-Sep 18:59</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13-Sep 13:30</t>
+          <t>13-Sep 18:57</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>13-Sep 13:32</t>
+          <t>13-Sep 18:59</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>13-Sep 13:32</t>
+          <t>13-Sep 18:57</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SS Retail IPOU</t>
+          <t>Jindal Supreme IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹110 (25.94%) 30 ↓ / 110 ↑</t>
+          <t>₹27 (29.03%) 11 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -506,17 +506,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>13-Sep 18:59</t>
+          <t>14-Sep 13:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13-Sep 18:57</t>
+          <t>14-Sep 13:56</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOU</t>
+          <t>SS Retail IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹25 (26.88%) 11 ↓ / 25 ↑</t>
+          <t>₹136 (32.08%) 30 ↓ / 136 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -640,17 +640,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>13-Sep 18:59</t>
+          <t>14-Sep 13:55</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>13-Sep 18:57</t>
+          <t>14-Sep 14:01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>14-Sep 13:55</t>
+          <t>14-Sep 20:59</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹24 (28.57%) 8 ↓ / 24 ↑</t>
+          <t>₹22 (26.19%) 8 ↓ / 24 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>14-Sep 13:56</t>
+          <t>14-Sep 20:54</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹136 (32.08%) 30 ↓ / 136 ↑</t>
+          <t>₹140 (33.02%) 30 ↓ / 140 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14-Sep 13:55</t>
+          <t>14-Sep 21:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>14-Sep 14:01</t>
+          <t>14-Sep 20:58</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>14-Sep 20:59</t>
+          <t>15-Sep 14:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>14-Sep 20:54</t>
+          <t>15-Sep 13:56</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹140 (33.02%) 30 ↓ / 140 ↑</t>
+          <t>₹145 (34.20%) 30 ↓ / 145 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -675,77 +675,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14-Sep 21:00</t>
+          <t>15-Sep 13:58</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Manika Plastech IPOO</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>₹11 (25.58%) 7 ↓ / 20 ↑</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1.49x</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>₹125.50 Cr</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>11-Sep GMP: 7</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>16-Sep</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>17-Sep</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>21-Sep</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>14-Sep 20:58</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOU</t>
+          <t>SS Retail IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹27 (29.03%) 11 ↓ / 27 ↑</t>
+          <t>₹145 (34.20%) 30 ↓ / 145 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -506,17 +506,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹124.88 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>15-Sep 14:00</t>
+          <t>15-Sep 19:32</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15-Sep 13:56</t>
+          <t>15-Sep 19:28</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SS Retail IPOU</t>
+          <t>Jindal Supreme IPOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹145 (34.20%) 30 ↓ / 145 ↑</t>
+          <t>₹27 (29.03%) 11 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -640,17 +640,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>15-Sep 13:58</t>
+          <t>15-Sep 19:34</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SS Retail IPOU</t>
+          <t>Jindal Supreme IPOO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹145 (34.20%) 30 ↓ / 145 ↑</t>
+          <t>₹24 (25.81%) 11 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,27 +501,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.23x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>93</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹500.00 Cr</t>
+          <t>₹124.88 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>161</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>16-Sep GMP: 24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>15-Sep 19:32</t>
+          <t>16-Sep 12:53</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hero Motors IPOU</t>
+          <t>SS Retail IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹22 (26.19%) 8 ↓ / 24 ↑</t>
+          <t>₹105 (24.76%) 30 ↓ / 140 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,27 +568,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.77x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>424</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹1000.00 Cr</t>
+          <t>₹500.00 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>35</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>16-Sep</t>
+          <t>16-Sep GMP: 105</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,77 +608,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15-Sep 19:28</t>
+          <t>16-Sep 12:57</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Jindal Supreme IPOU</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹27 (29.03%) 11 ↓ / 27 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹124.88 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>16-Sep</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>18-Sep</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>21-Sep</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>23-Sep</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>15-Sep 19:34</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹24 (25.81%) 11 ↓ / 27 ↑</t>
+          <t>₹25 (26.88%) 11 ↓ / 27 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.23x</t>
+          <t>7.56x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 24</t>
+          <t>16-Sep GMP: 25</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16-Sep 12:53</t>
+          <t>16-Sep 18:54</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹105 (24.76%) 30 ↓ / 140 ↑</t>
+          <t>₹100 (23.58%) 30 ↓ / 140 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.77x</t>
+          <t>1.52x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 105</t>
+          <t>16-Sep GMP: 100</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-Sep 12:57</t>
+          <t>16-Sep 18:57</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹25 (26.88%) 11 ↓ / 27 ↑</t>
+          <t>₹28 (30.11%) 11 ↓ / 28 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.56x</t>
+          <t>21.26x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16-Sep 18:54</t>
+          <t>17-Sep 13:55</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹100 (23.58%) 30 ↓ / 140 ↑</t>
+          <t>₹127 (29.95%) 30 ↓ / 140 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.52x</t>
+          <t>3.98x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>16-Sep GMP: 100</t>
+          <t>16-Sep GMP: 90</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-Sep 18:57</t>
+          <t>17-Sep 14:01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹28 (30.11%) 11 ↓ / 28 ↑</t>
+          <t>₹30 (32.26%) 11 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21.26x</t>
+          <t>31.54x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>17-Sep 13:55</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹127 (29.95%) 30 ↓ / 140 ↑</t>
+          <t>₹132 (31.13%) 30 ↓ / 140 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.98x</t>
+          <t>6.1x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>17-Sep 14:01</t>
+          <t>17-Sep 19:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jindal Supreme IPOO</t>
+          <t>Jindal Supreme IPOCT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹30 (32.26%) 11 ↓ / 30 ↑</t>
+          <t>₹33 (35.48%) 11 ↓ / 33 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>31.54x</t>
+          <t>135.05x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>18-Sep GMP: 33</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SS Retail IPOO</t>
+          <t>SS Retail IPOCT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹132 (31.13%) 30 ↓ / 140 ↑</t>
+          <t>₹149 (35.14%) 30 ↓ / 149 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.1x</t>
+          <t>45.84x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>18-Sep</t>
+          <t>18-Sep GMP: 149</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>17-Sep 19:37</t>
+          <t>18-Sep 13:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,140 +480,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Jindal Supreme IPOCT</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹33 (35.48%) 11 ↓ / 33 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>135.05x</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>₹124.88 Cr</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>16-Sep GMP: 25</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>18-Sep GMP: 33</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>21-Sep</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>23-Sep</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>18-Sep 13:37</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SS Retail IPOCT</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹149 (35.14%) 30 ↓ / 149 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>45.84x</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹500.00 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>16-Sep GMP: 90</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>18-Sep GMP: 149</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>21-Sep</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>23-Sep</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>18-Sep 13:37</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,73 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Adroit Industries IPOU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹37 (27.61%) 37 ↓ / 37 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹150.71 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>23-Sep</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25-Sep</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>28-Sep</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>30-Sep</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>19-Sep 13:02</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹37 (27.61%) 37 ↓ / 37 ↑</t>
+          <t>₹41 (30.60%) 37 ↓ / 41 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19-Sep 13:02</t>
+          <t>19-Sep 18:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹41 (30.60%) 37 ↓ / 41 ↑</t>
+          <t>₹35 (26.12%) 35 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19-Sep 18:02</t>
+          <t>20-Sep 13:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20-Sep 13:37</t>
+          <t>20-Sep 18:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹35 (26.12%) 35 ↓ / 37 ↑</t>
+          <t>₹32 (23.88%) 32 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20-Sep 18:37</t>
+          <t>21-Sep 14:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>21-Sep 14:02</t>
+          <t>21-Sep 21:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOU</t>
+          <t>Moneyview IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹32 (23.88%) 32 ↓ / 37 ↑</t>
+          <t>₹8.5 (25.00%) 5 ↓ / 8.50 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -506,42 +506,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹150.71 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>24-Sep</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>21-Sep 21:02</t>
+          <t>22-Sep 13:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹8.5 (25.00%) 5 ↓ / 8.50 ↑</t>
+          <t>₹10 (29.41%) 5 ↓ / 10 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,10 +541,77 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>22-Sep 13:37</t>
+          <t>22-Sep 19:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Adroit Industries IPOU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹32 (23.88%) 32 ↓ / 37 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹150.71 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>23-Sep</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25-Sep</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>28-Sep</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>30-Sep</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>22-Sep 19:02</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹10 (29.41%) 5 ↓ / 10 ↑</t>
+          <t>₹12.5 (36.76%) 5 ↓ / 12.50 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOU</t>
+          <t>Adroit Industries IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹32 (23.88%) 32 ↓ / 37 ↑</t>
+          <t>₹33 (24.63%) 32 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.89x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>23-Sep</t>
+          <t>23-Sep GMP: 33</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>22-Sep 19:02</t>
+          <t>23-Sep 13:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹12.5 (36.76%) 5 ↓ / 12.50 ↑</t>
+          <t>₹14 (41.18%) 5 ↓ / 14 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹33 (24.63%) 32 ↓ / 37 ↑</t>
+          <t>₹35 (26.12%) 32 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.89x</t>
+          <t>5.22x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 33</t>
+          <t>23-Sep GMP: 35</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>23-Sep 13:37</t>
+          <t>23-Sep 19:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Moneyview IPOU</t>
+          <t>Moneyview IPOO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24-Sep</t>
+          <t>24-Sep GMP: 14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹35 (26.12%) 32 ↓ / 37 ↑</t>
+          <t>₹34 (25.37%) 32 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>23-Sep GMP: 35</t>
+          <t>23-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>23-Sep 19:02</t>
+          <t>24-Sep 9:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Moneyview IPOO</t>
+          <t>German Green Steel IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹14 (41.18%) 5 ↓ / 14 ↑</t>
+          <t>₹28.5 (20.50%) 15 ↓ / 28.50 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -506,42 +506,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹1091.68 Cr</t>
+          <t>₹303.90 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 14</t>
+          <t>25-Sep</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>29-Sep</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>24-Sep 9:37</t>
+          <t>24-Sep 16:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,65 +553,199 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Orient Cables IPOU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹58 (21.32%) 34 ↓ / 58 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹552.00 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>25-Sep</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>29-Sep</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>30-Sep</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>5-Oct</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>24-Sep 16:02</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Moneyview IPOO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹12.75 (37.50%) 5 ↓ / 14 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.26x</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>₹1091.68 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>24-Sep GMP: 12.75</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>28-Sep</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>29-Sep</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1-Oct</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>24-Sep 16:02</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Adroit Industries IPOO</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>₹34 (25.37%) 32 ↓ / 37 ↑</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>5.22x</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>16.48x</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>₹150.71 Cr</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>23-Sep GMP: 34</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>25-Sep</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>28-Sep</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>30-Sep</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>24-Sep 9:37</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>24-Sep 16:02</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>German Green Steel IPOU</t>
+          <t>Orient Cables IPOO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹28.5 (20.50%) 15 ↓ / 28.50 ↑</t>
+          <t>₹70 (25.74%) 34 ↓ / 113 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,27 +501,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.26x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹303.90 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 70</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Orient Cables IPOU</t>
+          <t>German Green Steel IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹58 (21.32%) 34 ↓ / 58 ↑</t>
+          <t>₹31.5 (22.66%) 15 ↓ / 31.50 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,27 +568,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.09x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>139</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹552.00 Cr</t>
+          <t>₹303.90 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 31.5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹12.75 (37.50%) 5 ↓ / 14 ↑</t>
+          <t>₹14 (41.18%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.26x</t>
+          <t>4.41x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>24-Sep GMP: 12.75</t>
+          <t>24-Sep GMP: 15.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -687,12 +687,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Adroit Industries IPOO</t>
+          <t>Adroit Industries IPOCT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>₹34 (25.37%) 32 ↓ / 37 ↑</t>
+          <t>₹37 (27.61%) 32 ↓ / 37 ↑</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16.48x</t>
+          <t>96.73x</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25-Sep</t>
+          <t>25-Sep GMP: 37</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>24-Sep 16:02</t>
+          <t>25-Sep 14:02</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹70 (25.74%) 34 ↓ / 113 ↑</t>
+          <t>₹72 (26.47%) 34 ↓ / 113 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.26x</t>
+          <t>2.07x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 70</t>
+          <t>25-Sep GMP: 72</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹31.5 (22.66%) 15 ↓ / 31.50 ↑</t>
+          <t>₹28 (20.14%) 15 ↓ / 29 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.09x</t>
+          <t>1.82x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 31.5</t>
+          <t>25-Sep GMP: 28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.41x</t>
+          <t>6.22x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -675,77 +675,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25-Sep 14:02</t>
+          <t>25-Sep 19:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Adroit Industries IPOCT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>₹37 (27.61%) 32 ↓ / 37 ↑</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>96.73x</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>₹150.71 Cr</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>23-Sep GMP: 34</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25-Sep GMP: 37</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>28-Sep</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>30-Sep</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>25-Sep 14:02</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Orient Cables IPOO</t>
+          <t>SRIT India IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹72 (26.47%) 34 ↓ / 113 ↑</t>
+          <t>₹32 (24.62%) 12 ↓ / 32 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,47 +501,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.07x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹552.00 Cr</t>
+          <t>₹218.40 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 72</t>
+          <t>28-Sep</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>29-Sep</t>
+          <t>30-Sep</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>German Green Steel IPOO</t>
+          <t>Orient Cables IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹28 (20.14%) 15 ↓ / 29 ↑</t>
+          <t>₹85 (31.25%) 34 ↓ / 113 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,27 +568,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.82x</t>
+          <t>2.07x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹303.90 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 28</t>
+          <t>25-Sep GMP: 80</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹14 (41.18%) 5 ↓ / 15.50 ↑</t>
+          <t>₹13.75 (40.44%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>25-Sep 19:37</t>
+          <t>26-Sep 13:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹85 (31.25%) 34 ↓ / 113 ↑</t>
+          <t>₹86 (31.62%) 34 ↓ / 113 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹13.75 (40.44%) 5 ↓ / 15.50 ↑</t>
+          <t>₹14 (41.18%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>26-Sep 13:37</t>
+          <t>26-Sep 19:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹32 (24.62%) 12 ↓ / 32 ↑</t>
+          <t>₹33 (25.38%) 12 ↓ / 33 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹86 (31.62%) 34 ↓ / 113 ↑</t>
+          <t>₹90 (33.09%) 34 ↓ / 113 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>26-Sep 19:02</t>
+          <t>27-Sep 14:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,65 +620,132 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>German Green Steel IPOO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹29 (20.86%) 15 ↓ / 29 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>1.82x</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>₹303.90 Cr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>25-Sep GMP: 26</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>29-Sep</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>30-Sep</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5-Oct</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>27-Sep 14:37</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Moneyview IPOO</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>₹14 (41.18%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>6.22x</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>₹1091.68 Cr</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>441</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>24-Sep GMP: 15.5</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>28-Sep</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>29-Sep</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>1-Oct</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>26-Sep 19:02</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>27-Sep 14:37</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>German Green Steel IPOO</t>
+          <t>Moneyview IPOO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹29 (20.86%) 15 ↓ / 29 ↑</t>
+          <t>₹14 (41.18%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,117 +635,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.82x</t>
+          <t>6.22x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>34</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹303.90 Cr</t>
+          <t>₹1091.68 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>441</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 26</t>
+          <t>24-Sep GMP: 15.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>28-Sep</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>29-Sep</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>30-Sep</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27-Sep 14:37</t>
+          <t>27-Sep 19:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Moneyview IPOO</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>₹14 (41.18%) 5 ↓ / 15.50 ↑</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>6.22x</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>₹1091.68 Cr</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>24-Sep GMP: 15.5</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>28-Sep</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>29-Sep</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>1-Oct</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>27-Sep 14:37</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SRIT India IPOU</t>
+          <t>SRIT India IPOO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹33 (25.38%) 12 ↓ / 33 ↑</t>
+          <t>₹34 (26.15%) 12 ↓ / 34 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.74x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 34</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹90 (33.09%) 34 ↓ / 113 ↑</t>
+          <t>₹80 (29.41%) 34 ↓ / 113 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.07x</t>
+          <t>7.15x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Moneyview IPOO</t>
+          <t>Moneyview IPOCT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹14 (41.18%) 5 ↓ / 15.50 ↑</t>
+          <t>₹12.5 (36.76%) 5 ↓ / 15.50 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.22x</t>
+          <t>72.81x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28-Sep</t>
+          <t>28-Sep GMP: 12.5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>27-Sep 19:37</t>
+          <t>28-Sep 15:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SRIT India IPOO</t>
+          <t>Orient Cables IPOCT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹34 (26.15%) 12 ↓ / 34 ↑</t>
+          <t>₹85 (31.25%) 34 ↓ / 113 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,184 +501,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74x</t>
+          <t>63.8x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>272</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹218.40 Cr</t>
+          <t>₹552.00 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>28-Sep GMP: 34</t>
+          <t>25-Sep GMP: 80</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>29-Sep GMP: 85</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>30-Sep</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1-Oct</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>6-Oct</t>
+          <t>5-Oct</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>28-Sep 15:02</t>
+          <t>29-Sep 15:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Orient Cables IPOO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹80 (29.41%) 34 ↓ / 113 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>7.15x</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹552.00 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>25-Sep GMP: 80</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>29-Sep</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>30-Sep</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>5-Oct</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>28-Sep 15:02</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Moneyview IPOCT</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹12.5 (36.76%) 5 ↓ / 15.50 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>72.81x</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹1091.68 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>24-Sep GMP: 15.5</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>28-Sep GMP: 12.5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>29-Sep</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>1-Oct</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>28-Sep 15:02</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Orient Cables IPOCT</t>
+          <t>SRIT India IPOCT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹85 (31.25%) 34 ↓ / 113 ↑</t>
+          <t>₹38 (29.23%) 12 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,47 +501,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>63.8x</t>
+          <t>69.98x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>130</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹552.00 Cr</t>
+          <t>₹218.40 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>25-Sep GMP: 80</t>
+          <t>28-Sep GMP: 33</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>29-Sep GMP: 85</t>
+          <t>30-Sep GMP: 38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>30-Sep</t>
+          <t>1-Oct</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>5-Oct</t>
+          <t>6-Oct</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>29-Sep 15:02</t>
+          <t>30-Sep 14:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,73 +480,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SRIT India IPOCT</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹38 (29.23%) 12 ↓ / 38 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>69.98x</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>₹218.40 Cr</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>28-Sep GMP: 33</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30-Sep GMP: 38</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1-Oct</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>6-Oct</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>30-Sep 14:37</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,6 +480,73 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>HD Fire Protect IPOU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹75 (27.68%) 75 ↓ / 80 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹712.31 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>13-Oct</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15-Oct</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>16-Oct</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>21-Oct</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>8-Oct 16:02</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
         </is>
       </c>
     </row>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹75 (27.68%) 75 ↓ / 80 ↑</t>
+          <t>₹73 (26.94%) 63 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>8-Oct 16:02</t>
+          <t>9-Oct 15:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>9-Oct 15:37</t>
+          <t>10-Oct 15:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹73 (26.94%) 63 ↓ / 80 ↑</t>
+          <t>₹77 (28.41%) 63 ↓ / 80 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>10-Oct 15:02</t>
+          <t>11-Oct 15:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,65 +486,199 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Tonbo Imaging India IPOU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹390 (55.71%) 270 ↓ / 390 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹852.18 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>15-Oct</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>19-Oct</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>21-Oct</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>23-Oct</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>12-Oct 16:02</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bonfiglioli Transmissions IPOU</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹153 (26.11%) 137 ↓ / 175 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹2533.66 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>15-Oct</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>19-Oct</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>21-Oct</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>23-Oct</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>12-Oct 16:02</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>HD Fire Protect IPOU</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹77 (28.41%) 63 ↓ / 80 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>₹83 (30.63%) 63 ↓ / 86 ↑</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>271</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>₹712.31 Cr</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>13-Oct</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>15-Oct</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>16-Oct</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>21-Oct</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>11-Oct 15:02</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>12-Oct 16:02</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹390 (55.71%) 270 ↓ / 390 ↑</t>
+          <t>₹468 (66.86%) 270 ↓ / 468 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>12-Oct 16:02</t>
+          <t>13-Oct 16:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹153 (26.11%) 137 ↓ / 175 ↑</t>
+          <t>₹161 (27.47%) 137 ↓ / 175 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>12-Oct 16:02</t>
+          <t>13-Oct 16:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HD Fire Protect IPOU</t>
+          <t>HD Fire Protect IPOO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹83 (30.63%) 63 ↓ / 86 ↑</t>
+          <t>₹89 (32.84%) 63 ↓ / 89 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.21x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹712.31 Cr</t>
+          <t>₹712.13 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13-Oct</t>
+          <t>13-Oct GMP: 89</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12-Oct 16:02</t>
+          <t>13-Oct 16:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹468 (66.86%) 270 ↓ / 468 ↑</t>
+          <t>₹500 (71.43%) 270 ↓ / 500 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>13-Oct 16:02</t>
+          <t>14-Oct 14:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹161 (27.47%) 137 ↓ / 175 ↑</t>
+          <t>₹182 (31.06%) 137 ↓ / 182 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13-Oct 16:02</t>
+          <t>14-Oct 14:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹89 (32.84%) 63 ↓ / 89 ↑</t>
+          <t>₹91 (33.58%) 63 ↓ / 91 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.21x</t>
+          <t>12.41x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13-Oct GMP: 89</t>
+          <t>13-Oct GMP: 91</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>13-Oct 16:02</t>
+          <t>14-Oct 14:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>14-Oct 14:02</t>
+          <t>14-Oct 19:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹182 (31.06%) 137 ↓ / 182 ↑</t>
+          <t>₹180 (30.72%) 137 ↓ / 180 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>14-Oct 14:02</t>
+          <t>14-Oct 19:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹91 (33.58%) 63 ↓ / 91 ↑</t>
+          <t>₹89 (32.84%) 63 ↓ / 91 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12.41x</t>
+          <t>16.56x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14-Oct 14:02</t>
+          <t>14-Oct 19:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tonbo Imaging India IPOU</t>
+          <t>Tonbo Imaging India IPOO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.27x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>15-Oct GMP: 500</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>14-Oct 19:37</t>
+          <t>15-Oct 13:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bonfiglioli Transmissions IPOU</t>
+          <t>Bonfiglioli Transmissions IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹180 (30.72%) 137 ↓ / 180 ↑</t>
+          <t>₹173 (29.52%) 137 ↓ / 178 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.28x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>15-Oct GMP: 173</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>14-Oct 19:37</t>
+          <t>15-Oct 13:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HD Fire Protect IPOO</t>
+          <t>HD Fire Protect IPOCT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹89 (32.84%) 63 ↓ / 91 ↑</t>
+          <t>₹82 (30.26%) 63 ↓ / 91 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16.56x</t>
+          <t>52.49x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15-Oct</t>
+          <t>15-Oct GMP: 82</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>14-Oct 19:37</t>
+          <t>15-Oct 13:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rating▲▼</t>
+          <t>🔥Rating▲▼</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -486,62 +486,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tonbo Imaging India IPOO</t>
+          <t>Jio Platforms IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹500 (71.43%) 270 ↓ / 500 ↑</t>
+          <t>₹229 (20.46%) 148 ↓ / 229 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.27x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹852.18 Cr</t>
+          <t>₹30213.00 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>15-Oct GMP: 500</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>19-Oct</t>
+          <t>23-Oct</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>21-Oct</t>
+          <t>26-Oct</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>23-Oct</t>
+          <t>28-Oct</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>15-Oct 13:37</t>
+          <t>15-Oct 19:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,42 +553,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bonfiglioli Transmissions IPOO</t>
+          <t>Tonbo Imaging India IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹173 (29.52%) 137 ↓ / 178 ↑</t>
+          <t>₹495 (70.71%) 270 ↓ / 500 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.28x</t>
+          <t>4.01x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹2533.66 Cr</t>
+          <t>₹852.18 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>15-Oct GMP: 173</t>
+          <t>15-Oct GMP: 495</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15-Oct 13:37</t>
+          <t>15-Oct 19:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HD Fire Protect IPOCT</t>
+          <t>Bonfiglioli Transmissions IPOO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹82 (30.26%) 63 ↓ / 91 ↑</t>
+          <t>₹147 (25.09%) 137 ↓ / 178 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,47 +635,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>52.49x</t>
+          <t>0.48x</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>586</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>₹712.13 Cr</t>
+          <t>₹2533.66 Cr</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13-Oct GMP: 91</t>
+          <t>15-Oct GMP: 147</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>15-Oct GMP: 82</t>
+          <t>19-Oct</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16-Oct</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>21-Oct</t>
+          <t>23-Oct</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>15-Oct 13:37</t>
+          <t>15-Oct 19:02</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,62 +486,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jio Platforms IPOU</t>
+          <t>Tonbo Imaging India IPOO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹229 (20.46%) 148 ↓ / 229 ↑</t>
+          <t>₹500 (71.43%) 270 ↓ / 500 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.6x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>700</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹30213.00 Cr</t>
+          <t>₹852.18 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>15-Oct GMP: 500</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>19-Oct</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>21-Oct</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>23-Oct</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>26-Oct</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>28-Oct</t>
-        </is>
-      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>15-Oct 19:02</t>
+          <t>16-Oct 12:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,42 +553,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tonbo Imaging India IPOO</t>
+          <t>Bonfiglioli Transmissions IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹495 (70.71%) 270 ↓ / 500 ↑</t>
+          <t>₹138 (23.55%) 137 ↓ / 178 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.01x</t>
+          <t>0.68x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>586</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>₹852.18 Cr</t>
+          <t>₹2533.66 Cr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>15-Oct GMP: 495</t>
+          <t>15-Oct GMP: 140</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,77 +608,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15-Oct 19:02</t>
+          <t>16-Oct 12:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Bonfiglioli Transmissions IPOO</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹147 (25.09%) 137 ↓ / 178 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.48x</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹2533.66 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>15-Oct GMP: 147</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>19-Oct</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>21-Oct</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>23-Oct</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>15-Oct 19:02</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.6x</t>
+          <t>7.78x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16-Oct 12:02</t>
+          <t>16-Oct 19:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹138 (23.55%) 137 ↓ / 178 ↑</t>
+          <t>₹128 (21.84%) 128 ↓ / 178 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.68x</t>
+          <t>0.99x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-Oct 12:02</t>
+          <t>16-Oct 19:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹500 (71.43%) 270 ↓ / 500 ↑</t>
+          <t>₹520 (74.29%) 270 ↓ / 520 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>16-Oct 19:02</t>
+          <t>17-Oct 13:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹128 (21.84%) 128 ↓ / 178 ↑</t>
+          <t>₹131 (22.35%) 129 ↓ / 178 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>16-Oct 19:02</t>
+          <t>17-Oct 13:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹520 (74.29%) 270 ↓ / 520 ↑</t>
+          <t>₹505 (72.14%) 270 ↓ / 516 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>17-Oct 13:02</t>
+          <t>17-Oct 18:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹131 (22.35%) 129 ↓ / 178 ↑</t>
+          <t>₹132 (22.53%) 129 ↓ / 178 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>17-Oct 13:02</t>
+          <t>17-Oct 18:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,62 +486,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tonbo Imaging India IPOO</t>
+          <t>Jio Platforms IPOU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹505 (72.14%) 270 ↓ / 516 ↑</t>
+          <t>₹242 (21.63%) 148 ↓ / 242 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥🔥🔥</t>
+          <t>🔥🔥🔥🔥</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.78x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹852.18 Cr</t>
+          <t>₹30213.00 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>15-Oct GMP: 500</t>
+          <t>21-Oct</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>19-Oct</t>
+          <t>23-Oct</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>21-Oct</t>
+          <t>26-Oct</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>23-Oct</t>
+          <t>28-Oct</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>17-Oct 18:02</t>
+          <t>18-Oct 13:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,65 +553,132 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Tonbo Imaging India IPOO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹505 (72.14%) 270 ↓ / 516 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>7.78x</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>₹852.18 Cr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>15-Oct GMP: 500</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>19-Oct</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>21-Oct</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>23-Oct</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>18-Oct 13:02</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Bonfiglioli Transmissions IPOO</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>₹132 (22.53%) 129 ↓ / 178 ↑</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.99x</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>586</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>₹2533.66 Cr</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>15-Oct GMP: 140</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>19-Oct</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>21-Oct</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>23-Oct</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>17-Oct 18:02</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>18-Oct 13:02</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹242 (21.63%) 148 ↓ / 242 ↑</t>
+          <t>₹249 (22.25%) 148 ↓ / 249 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>18-Oct 13:02</t>
+          <t>18-Oct 18:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹505 (72.14%) 270 ↓ / 516 ↑</t>
+          <t>₹515 (73.57%) 270 ↓ / 516 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18-Oct 13:02</t>
+          <t>18-Oct 18:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>₹132 (22.53%) 129 ↓ / 178 ↑</t>
+          <t>₹130 (22.18%) 129 ↓ / 178 ↑</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>18-Oct 13:02</t>
+          <t>18-Oct 18:37</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹249 (22.25%) 148 ↓ / 249 ↑</t>
+          <t>₹252 (22.52%) 148 ↓ / 252 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>18-Oct 18:37</t>
+          <t>19-Oct 14:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tonbo Imaging India IPOO</t>
+          <t>Tonbo Imaging India IPOCT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>7.78x</t>
+          <t>53.59x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>19-Oct</t>
+          <t>19-Oct GMP: 515</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -608,77 +608,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>18-Oct 18:37</t>
+          <t>19-Oct 14:02</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Bonfiglioli Transmissions IPOO</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>₹130 (22.18%) 129 ↓ / 178 ↑</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>0.99x</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>₹2533.66 Cr</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>15-Oct GMP: 140</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>19-Oct</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>21-Oct</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>23-Oct</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>18-Oct 18:37</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹252 (22.52%) 148 ↓ / 252 ↑</t>
+          <t>₹253 (22.61%) 148 ↓ / 253 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,77 +541,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19-Oct 14:02</t>
+          <t>19-Oct 21:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tonbo Imaging India IPOCT</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹515 (73.57%) 270 ↓ / 516 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>53.59x</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹852.18 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>15-Oct GMP: 500</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>19-Oct GMP: 515</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>21-Oct</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>23-Oct</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>19-Oct 14:02</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹253 (22.61%) 148 ↓ / 253 ↑</t>
+          <t>₹247 (22.07%) 148 ↓ / 250 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>19-Oct 21:37</t>
+          <t>20-Oct 13:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,65 +486,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>BLS Polymers IPOU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹37 (24.67%) 18 ↓ / 37 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹255.00 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>27-Oct</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>29-Oct</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>30-Oct</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3-Nov</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>20-Oct 19:37</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Jio Platforms IPOU</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹247 (22.07%) 148 ↓ / 250 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹259 (23.15%) 148 ↓ / 259 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1119</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>₹30213.00 Cr</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>21-Oct</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>23-Oct</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>26-Oct</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>28-Oct</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>20-Oct 13:37</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>20-Oct 19:37</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹37 (24.67%) 18 ↓ / 37 ↑</t>
+          <t>₹30 (20.00%) 18 ↓ / 30 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>20-Oct 19:37</t>
+          <t>21-Oct 13:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jio Platforms IPOU</t>
+          <t>Jio Platforms IPOO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹259 (23.15%) 148 ↓ / 259 ↑</t>
+          <t>₹255 (22.79%) 148 ↓ / 273 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.72x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>21-Oct</t>
+          <t>21-Oct GMP: 255</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>20-Oct 19:37</t>
+          <t>21-Oct 13:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>21-Oct 13:37</t>
+          <t>21-Oct 19:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹255 (22.79%) 148 ↓ / 273 ↑</t>
+          <t>₹249 (22.25%) 148 ↓ / 273 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.72x</t>
+          <t>3.04x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>21-Oct GMP: 255</t>
+          <t>21-Oct GMP: 249</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>21-Oct 13:37</t>
+          <t>21-Oct 19:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BLS Polymers IPOU</t>
+          <t>Jio Platforms IPOO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹30 (20.00%) 18 ↓ / 30 ↑</t>
+          <t>₹241 (21.54%) 148 ↓ / 273 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,117 +501,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.14x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>₹255.00 Cr</t>
+          <t>₹30213.00 Cr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>27-Oct</t>
+          <t>21-Oct GMP: 246</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>29-Oct</t>
+          <t>23-Oct</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>30-Oct</t>
+          <t>26-Oct</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3-Nov</t>
+          <t>28-Oct</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>21-Oct 19:37</t>
+          <t>22-Oct 14:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Jio Platforms IPOO</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹249 (22.25%) 148 ↓ / 273 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>3.04x</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1119</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹30213.00 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>21-Oct GMP: 249</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>23-Oct</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>26-Oct</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>28-Oct</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>21-Oct 19:37</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,65 +486,132 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>BLS Polymers IPOU</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>₹38 (25.33%) 18 ↓ / 38 ↑</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🔥🔥🔥🔥</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>₹255.00 Cr</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>27-Oct</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>29-Oct</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>30-Oct</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3-Nov</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>22-Oct 19:37</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Jio Platforms IPOO</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹241 (21.54%) 148 ↓ / 273 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>₹244 (21.81%) 148 ↓ / 273 ↑</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>🔥🔥🔥🔥</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>4.14x</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5.4x</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>1119</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>₹30213.00 Cr</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>21-Oct GMP: 246</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>23-Oct</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>26-Oct</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>28-Oct</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>22-Oct 14:02</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>22-Oct 19:37</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>22-Oct 19:37</t>
+          <t>23-Oct 13:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -553,12 +553,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jio Platforms IPOO</t>
+          <t>Jio Platforms IPOCT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>₹244 (21.81%) 148 ↓ / 273 ↑</t>
+          <t>₹254 (22.70%) 148 ↓ / 273 ↑</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.4x</t>
+          <t>9.1x</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>23-Oct</t>
+          <t>23-Oct GMP: 254</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>22-Oct 19:37</t>
+          <t>23-Oct 13:37</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,77 +541,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23-Oct 13:37</t>
+          <t>23-Oct 19:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Jio Platforms IPOCT</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>₹254 (22.70%) 148 ↓ / 273 ↑</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>9.1x</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1119</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>₹30213.00 Cr</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>21-Oct GMP: 246</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>23-Oct GMP: 254</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>26-Oct</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>28-Oct</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>23-Oct 13:37</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹38 (25.33%) 18 ↓ / 38 ↑</t>
+          <t>₹33 (22.00%) 18 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>23-Oct 19:37</t>
+          <t>24-Oct 13:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹33 (22.00%) 18 ↓ / 38 ↑</t>
+          <t>₹39 (26.00%) 18 ↓ / 39 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>24-Oct 13:37</t>
+          <t>24-Oct 18:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹39 (26.00%) 18 ↓ / 39 ↑</t>
+          <t>₹38 (25.33%) 18 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>24-Oct 18:37</t>
+          <t>25-Oct 13:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>25-Oct 13:37</t>
+          <t>25-Oct 19:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹38 (25.33%) 18 ↓ / 38 ↑</t>
+          <t>₹33 (22.00%) 18 ↓ / 38 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>25-Oct 19:02</t>
+          <t>26-Oct 14:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹33 (22.00%) 18 ↓ / 38 ↑</t>
+          <t>₹40 (26.67%) 18 ↓ / 40 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>26-Oct 14:02</t>
+          <t>26-Oct 21:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BLS Polymers IPOU</t>
+          <t>BLS Polymers IPOO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹40 (26.67%) 18 ↓ / 40 ↑</t>
+          <t>₹43 (28.67%) 18 ↓ / 43 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.5x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>27-Oct</t>
+          <t>27-Oct GMP: 43</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>26-Oct 21:02</t>
+          <t>27-Oct 14:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹43 (28.67%) 18 ↓ / 43 ↑</t>
+          <t>₹44 (29.33%) 18 ↓ / 44 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.5x</t>
+          <t>9.62x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>27-Oct GMP: 43</t>
+          <t>27-Oct GMP: 44</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-Oct 14:37</t>
+          <t>27-Oct 20:37</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹44 (29.33%) 18 ↓ / 44 ↑</t>
+          <t>₹47 (31.33%) 18 ↓ / 47 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.62x</t>
+          <t>28.09x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>27-Oct 20:37</t>
+          <t>28-Oct 15:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BLS Polymers IPOO</t>
+          <t>BLS Polymers IPOCT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>₹47 (31.33%) 18 ↓ / 47 ↑</t>
+          <t>₹60 (40.00%) 18 ↓ / 60 ↑</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>28.09x</t>
+          <t>198.7x</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>29-Oct</t>
+          <t>29-Oct GMP: 60</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>28-Oct 15:02</t>
+          <t>29-Oct 15:02</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">

--- a/files/Mainboard_IPOs.xlsx
+++ b/files/Mainboard_IPOs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,73 +480,6 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>Anchor▲▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BLS Polymers IPOCT</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>₹60 (40.00%) 18 ↓ / 60 ↑</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>🔥🔥🔥🔥</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>198.7x</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>₹255.00 Cr</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>27-Oct GMP: 44</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>29-Oct GMP: 60</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>30-Oct</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>3-Nov</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>29-Oct 15:02</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>✅</t>
         </is>
       </c>
     </row>
